--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-24T11:26:43+00:00</t>
+    <t>2025-01-29T08:49:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T08:49:29+00:00</t>
+    <t>2025-01-29T12:34:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
+++ b/r4-ELGA-AustrianPatientSummary-AG-IV-APS/ValueSet-at-ips-laboratory-pathology-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-29T12:34:29+00:00</t>
+    <t>2025-02-03T12:54:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
